--- a/src/vlinder/data/refugee/xlsx/refugee.xlsx
+++ b/src/vlinder/data/refugee/xlsx/refugee.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/tRBS/open source/trbs-refugee-2/trbs-add-refugee/model/data/refugee/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tdijk004/Documents/Tooling/tRBS/open source/trbs/src/vlinder/data/refugee/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E89EA71-60BF-0F4C-A7C6-D577FEDFF97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41BD19A-BFC8-A64B-A152-B403AA452F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="2460" windowWidth="31660" windowHeight="15880" activeTab="5" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
+    <workbookView xWindow="860" yWindow="2460" windowWidth="31660" windowHeight="15880" xr2:uid="{4D223BC5-A265-7B41-9F5C-066E948A074C}"/>
   </bookViews>
   <sheets>
     <sheet name="configurations" sheetId="1" r:id="rId1"/>
@@ -656,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -664,7 +664,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -694,9 +693,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -734,7 +733,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -840,7 +839,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -982,7 +981,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1009,7 +1008,7 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3056,16 +3055,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
+      <c r="A61" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" t="s">
         <v>53</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" t="s">
         <v>164</v>
       </c>
     </row>
